--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -12369,6 +12369,154 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>167</v>
+      </c>
+      <c r="O68" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.136407004063483</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA68" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB68" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12402,7 +12550,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12633,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
@@ -12495,7 +12643,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
@@ -12547,7 +12695,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3832</v>
+        <v>3999</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -768,9 +768,6 @@
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -1318,9 +1315,6 @@
       <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -1868,9 +1862,6 @@
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -2418,9 +2409,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2968,9 +2956,6 @@
       <c r="P14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3518,9 +3503,6 @@
       <c r="P17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4068,9 +4050,6 @@
       <c r="P20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4618,9 +4597,6 @@
       <c r="P23" t="n">
         <v>1</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -5168,9 +5144,6 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5718,9 +5691,6 @@
       <c r="P29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -6268,9 +6238,6 @@
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6818,9 +6785,6 @@
       <c r="P35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -7368,9 +7332,6 @@
       <c r="P38" t="n">
         <v>3</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.7456584039430416</v>
       </c>
@@ -7918,9 +7879,6 @@
       <c r="P41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8468,9 +8426,6 @@
       <c r="P44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -9018,9 +8973,6 @@
       <c r="P47" t="n">
         <v>0</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
@@ -9568,9 +9520,6 @@
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2485528013143472</v>
       </c>
@@ -10118,9 +10067,6 @@
       <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -11109,9 +11055,6 @@
       <c r="O59" t="n">
         <v>112</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.09148254164736583</v>
       </c>
@@ -11257,9 +11200,6 @@
       <c r="O60" t="n">
         <v>97</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.07923041553387933</v>
       </c>
@@ -11405,9 +11345,6 @@
       <c r="O61" t="n">
         <v>102</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.08331445757170816</v>
       </c>
@@ -11553,9 +11490,6 @@
       <c r="O62" t="n">
         <v>110</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.08984892483223429</v>
       </c>
@@ -11701,9 +11635,6 @@
       <c r="O63" t="n">
         <v>108</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.08821530801710276</v>
       </c>
@@ -11849,9 +11780,6 @@
       <c r="O64" t="n">
         <v>126</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1029178593532865</v>
       </c>
@@ -11997,9 +11925,6 @@
       <c r="O65" t="n">
         <v>127</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.1037346677608523</v>
       </c>
@@ -12145,9 +12070,6 @@
       <c r="O66" t="n">
         <v>191</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.1560104058450614</v>
       </c>
@@ -12293,9 +12215,6 @@
       <c r="O67" t="n">
         <v>178</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.1453918965467064</v>
       </c>
@@ -12440,9 +12359,6 @@
       </c>
       <c r="O68" t="n">
         <v>167</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
       </c>
       <c r="R68" t="n">
         <v>0.136407004063483</v>

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -12433,6 +12433,151 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>192</v>
+      </c>
+      <c r="O69" t="n">
+        <v>192</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.1568272142526271</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12466,7 +12611,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -12549,7 +12694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -12559,7 +12704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -12611,7 +12756,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3999</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -12578,6 +12578,151 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>215</v>
+      </c>
+      <c r="O70" t="n">
+        <v>215</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.1756138076266398</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA70" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB70" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC70" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12611,7 +12756,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12694,7 +12839,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -12704,7 +12849,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -12756,7 +12901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4191</v>
+        <v>4406</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d140/2026-2029.xlsx
+++ b/diseases/d140/2026-2029.xlsx
@@ -12723,6 +12723,151 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>mycoplasma-pneumonia</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D140</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Mycoplasma pneumonia</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>支原体肺炎</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>211</v>
+      </c>
+      <c r="O71" t="n">
+        <v>211</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.1723465739963767</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12756,7 +12901,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -12839,7 +12984,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -12849,7 +12994,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11">
@@ -12901,7 +13046,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4406</v>
+        <v>4617</v>
       </c>
     </row>
     <row r="16">
